--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="480">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,6 +293,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,6 +437,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -474,7 +481,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -554,7 +561,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -590,7 +597,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -696,72 +703,72 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -789,7 +796,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -830,7 +837,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -888,7 +895,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -919,7 +926,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -972,7 +979,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1111,10 +1118,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1234,7 +1241,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1400,7 +1407,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1422,7 +1429,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1437,10 +1444,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1484,7 +1495,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2117,7 +2128,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2125,10 +2136,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2139,7 +2150,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2148,19 +2159,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2210,13 +2221,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2245,10 +2256,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2259,7 +2270,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2268,16 +2279,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2328,19 +2339,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2363,10 +2374,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2377,28 +2388,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2448,19 +2459,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2483,10 +2494,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2497,7 +2508,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2509,16 +2520,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2544,13 +2555,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2568,19 +2579,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2603,21 +2614,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2629,16 +2640,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2688,19 +2699,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2712,7 +2723,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2723,14 +2734,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2749,16 +2760,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2808,7 +2819,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2820,7 +2831,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2832,7 +2843,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2843,14 +2854,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2869,16 +2880,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2928,7 +2939,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2940,7 +2951,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2952,7 +2963,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2963,14 +2974,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2983,25 +2994,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3050,7 +3061,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3062,7 +3073,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3074,7 +3085,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3085,10 +3096,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3108,20 +3119,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3170,7 +3181,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3182,22 +3193,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3205,14 +3216,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3228,20 +3239,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3290,7 +3301,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3302,19 +3313,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3325,14 +3336,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3348,19 +3359,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3410,7 +3421,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3422,19 +3433,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3445,10 +3456,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3456,34 +3467,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3493,7 +3504,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3508,13 +3519,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3532,34 +3543,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3567,10 +3578,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3593,19 +3604,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3630,13 +3641,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3654,7 +3665,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3666,7 +3677,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3678,10 +3689,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3689,21 +3700,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3712,22 +3723,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3737,7 +3748,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3752,13 +3763,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3776,45 +3787,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3825,7 +3836,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3837,13 +3848,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3894,13 +3905,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3918,7 +3929,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3929,14 +3940,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3955,16 +3966,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4002,19 +4013,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4026,7 +4037,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4038,7 +4049,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4049,10 +4060,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4072,22 +4083,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4136,7 +4147,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4148,7 +4159,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4157,10 +4168,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4171,10 +4182,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4185,7 +4196,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4194,22 +4205,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4219,7 +4230,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4258,19 +4269,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4279,10 +4290,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4293,10 +4304,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4304,10 +4315,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4316,22 +4327,22 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4380,34 +4391,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4415,10 +4426,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4438,19 +4449,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4500,7 +4511,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4512,7 +4523,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4521,13 +4532,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4535,21 +4546,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4558,22 +4569,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4622,34 +4633,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4657,21 +4668,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4680,22 +4691,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4744,34 +4755,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4779,10 +4790,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4793,7 +4804,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4802,19 +4813,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4864,19 +4875,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4885,13 +4896,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4899,10 +4910,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4922,20 +4933,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4984,7 +4995,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4996,22 +5007,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5019,10 +5030,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5030,10 +5041,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5042,22 +5053,22 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5094,68 +5105,68 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5164,22 +5175,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5228,45 +5239,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5277,7 +5288,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5289,19 +5300,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5326,13 +5337,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5350,19 +5361,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5371,10 +5382,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5385,14 +5396,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5411,19 +5422,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5448,13 +5459,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5472,7 +5483,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5484,33 +5495,33 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5524,7 +5535,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5533,19 +5544,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5594,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5606,7 +5617,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5615,10 +5626,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5629,10 +5640,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5643,7 +5654,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5655,16 +5666,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5690,13 +5701,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5714,45 +5725,45 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5763,7 +5774,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5775,19 +5786,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5812,13 +5823,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5836,19 +5847,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5857,10 +5868,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5871,10 +5882,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5885,7 +5896,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5897,16 +5908,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5956,45 +5967,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6005,7 +6016,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6017,16 +6028,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6076,45 +6087,45 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6137,19 +6148,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6198,7 +6209,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6210,7 +6221,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6219,10 +6230,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6233,10 +6244,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6247,7 +6258,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6259,13 +6270,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6316,13 +6327,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6340,7 +6351,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6351,14 +6362,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6377,16 +6388,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6436,7 +6447,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6448,7 +6459,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6460,7 +6471,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6471,14 +6482,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6491,25 +6502,25 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6558,7 +6569,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6570,7 +6581,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6582,7 +6593,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6593,10 +6604,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6607,7 +6618,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6619,13 +6630,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6676,19 +6687,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6697,10 +6708,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6711,10 +6722,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6725,7 +6736,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6737,13 +6748,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6794,31 +6805,31 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6829,10 +6840,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6843,7 +6854,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6855,19 +6866,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6892,13 +6903,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6916,31 +6927,31 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6951,10 +6962,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6977,19 +6988,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7014,13 +7025,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7038,7 +7049,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7050,19 +7061,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7073,10 +7084,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7087,7 +7098,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7099,17 +7110,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7158,19 +7169,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7182,7 +7193,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7193,10 +7204,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7207,7 +7218,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7219,13 +7230,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7276,19 +7287,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7297,10 +7308,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7311,10 +7322,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7334,19 +7345,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7396,7 +7407,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7408,7 +7419,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7417,10 +7428,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7431,10 +7442,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7454,19 +7465,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7516,7 +7527,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7528,7 +7539,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7537,10 +7548,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7551,10 +7562,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7574,22 +7585,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7638,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7650,7 +7661,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>456</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7659,10 +7670,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7673,10 +7684,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7687,7 +7698,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7699,13 +7710,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7756,13 +7767,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7780,7 +7791,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7791,14 +7802,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7817,16 +7828,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7876,7 +7887,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7888,7 +7899,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7900,7 +7911,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7911,14 +7922,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7931,25 +7942,25 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7998,7 +8009,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8010,7 +8021,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8022,7 +8033,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8033,10 +8044,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8044,10 +8055,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8056,22 +8067,22 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8096,13 +8107,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8120,34 +8131,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8155,10 +8166,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8169,7 +8180,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8178,22 +8189,22 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8242,45 +8253,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8291,7 +8302,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8303,19 +8314,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8340,13 +8351,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8364,19 +8375,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8385,10 +8396,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8399,14 +8410,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8425,19 +8436,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8462,13 +8473,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8486,7 +8497,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8498,33 +8509,33 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8550,16 +8561,16 @@
         <v>83</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8608,7 +8619,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8620,7 +8631,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8629,10 +8640,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,9 +293,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -437,10 +434,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -481,7 +474,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -561,7 +554,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -597,7 +590,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -703,6 +696,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -765,10 +762,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -796,7 +789,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -837,7 +830,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -895,7 +888,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -926,7 +919,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -979,7 +972,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1118,10 +1111,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1241,7 +1234,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1407,7 +1400,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1429,7 +1422,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1444,14 +1437,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1495,7 +1484,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2128,7 +2117,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2136,10 +2125,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2150,28 +2139,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2221,13 +2210,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2256,10 +2245,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2270,25 +2259,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2339,19 +2328,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2374,10 +2363,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2388,28 +2377,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2459,19 +2448,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2494,10 +2483,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2508,7 +2497,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2520,16 +2509,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2555,43 +2544,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2614,21 +2603,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2640,16 +2629,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2699,31 +2688,31 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2734,14 +2723,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2760,16 +2749,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2819,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2831,7 +2820,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2843,7 +2832,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2854,14 +2843,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2880,16 +2869,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2939,7 +2928,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2951,7 +2940,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2963,7 +2952,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2974,14 +2963,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2994,25 +2983,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3061,7 +3050,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3073,7 +3062,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3085,7 +3074,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3096,10 +3085,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3119,20 +3108,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3181,7 +3170,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3193,22 +3182,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3216,14 +3205,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3239,20 +3228,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3301,7 +3290,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3313,19 +3302,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3336,14 +3325,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3359,19 +3348,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3421,7 +3410,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3433,19 +3422,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3456,10 +3445,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3467,34 +3456,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3504,73 +3493,73 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3578,10 +3567,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3604,19 +3593,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3641,13 +3630,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3665,7 +3654,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3677,7 +3666,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3689,10 +3678,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3700,45 +3689,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3748,84 +3737,84 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3836,7 +3825,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3848,13 +3837,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3905,31 +3894,31 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3940,14 +3929,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3966,16 +3955,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4013,19 +4002,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4037,7 +4026,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4049,7 +4038,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4060,10 +4049,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4083,22 +4072,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4147,7 +4136,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4159,7 +4148,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4168,10 +4157,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4182,10 +4171,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4196,31 +4185,31 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4230,70 +4219,70 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4304,10 +4293,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4315,34 +4304,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4391,34 +4380,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4426,10 +4415,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4449,19 +4438,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4511,7 +4500,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4523,7 +4512,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4532,13 +4521,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4546,45 +4535,45 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4633,34 +4622,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4668,45 +4657,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4755,34 +4744,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4790,10 +4779,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4804,28 +4793,28 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4875,19 +4864,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4896,13 +4885,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4910,10 +4899,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4933,20 +4922,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4995,7 +4984,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5007,22 +4996,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5030,10 +5019,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5041,34 +5030,34 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5105,92 +5094,92 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AF27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5239,45 +5228,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5288,7 +5277,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5300,19 +5289,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5337,55 +5326,55 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AJ29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5396,14 +5385,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5422,19 +5411,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5459,13 +5448,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5483,7 +5472,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5495,33 +5484,33 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5535,7 +5524,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5544,19 +5533,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5605,7 +5594,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5617,7 +5606,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5626,10 +5615,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5640,10 +5629,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5654,7 +5643,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5666,16 +5655,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5701,69 +5690,69 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>357</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5774,7 +5763,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5786,19 +5775,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5823,55 +5812,55 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5882,10 +5871,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5896,7 +5885,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5908,16 +5897,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5967,45 +5956,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>375</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6016,7 +6005,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6028,16 +6017,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6087,45 +6076,45 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6148,19 +6137,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6209,7 +6198,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6221,19 +6210,19 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6244,10 +6233,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6258,7 +6247,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6270,13 +6259,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6327,31 +6316,31 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6362,14 +6351,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6388,16 +6377,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6447,7 +6436,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6459,7 +6448,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6471,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6482,14 +6471,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6502,25 +6491,25 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6569,7 +6558,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6581,7 +6570,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6593,7 +6582,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6604,10 +6593,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6618,7 +6607,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6630,13 +6619,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6687,31 +6676,31 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6722,10 +6711,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6736,7 +6725,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6748,13 +6737,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6805,19 +6794,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6826,10 +6815,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6840,10 +6829,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6854,7 +6843,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6866,19 +6855,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6903,55 +6892,55 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6962,10 +6951,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6988,19 +6977,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7025,13 +7014,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7049,7 +7038,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7061,19 +7050,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7084,10 +7073,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7098,7 +7087,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7110,17 +7099,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7169,19 +7158,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7193,7 +7182,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7204,10 +7193,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7218,7 +7207,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7230,13 +7219,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7287,19 +7276,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7308,10 +7297,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7322,10 +7311,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7345,19 +7334,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7407,7 +7396,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7419,7 +7408,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7428,10 +7417,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7442,10 +7431,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7465,19 +7454,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7527,7 +7516,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7539,7 +7528,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7548,10 +7537,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7562,10 +7551,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7585,22 +7574,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7649,7 +7638,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7661,7 +7650,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>456</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7670,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7684,10 +7673,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7698,7 +7687,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7710,13 +7699,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7767,31 +7756,31 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7802,14 +7791,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7828,16 +7817,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7887,7 +7876,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7899,7 +7888,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7911,7 +7900,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7922,14 +7911,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7942,25 +7931,25 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8009,7 +7998,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8021,7 +8010,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8033,7 +8022,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8044,10 +8033,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8055,34 +8044,34 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G52" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8107,14 +8096,14 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8131,34 +8120,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8166,10 +8155,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8180,31 +8169,31 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8253,45 +8242,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8302,7 +8291,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8314,19 +8303,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8351,55 +8340,55 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z54" t="s" s="2">
+      <c r="AJ54" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8410,14 +8399,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8436,19 +8425,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8473,13 +8462,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8497,7 +8486,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8509,33 +8498,33 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8561,16 +8550,16 @@
         <v>83</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8619,7 +8608,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8631,7 +8620,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8640,10 +8629,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
